--- a/data/trans_orig/P36B08_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B08_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>311854</t>
+          <t>308104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>351856</t>
+          <t>348904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>211237</t>
+          <t>212723</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>242376</t>
+          <t>243326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>532880</t>
+          <t>532703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>583238</t>
+          <t>585164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121086</t>
+          <t>124038</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161088</t>
+          <t>164838</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64304</t>
+          <t>63354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95443</t>
+          <t>93957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196385</t>
+          <t>194459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246743</t>
+          <t>246920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>217764</t>
+          <t>218315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>253995</t>
+          <t>256362</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>237741</t>
+          <t>238111</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>273234</t>
+          <t>273703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>466842</t>
+          <t>465474</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>518458</t>
+          <t>518495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112939</t>
+          <t>110572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149170</t>
+          <t>148619</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98631</t>
+          <t>98162</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134124</t>
+          <t>133754</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>220341</t>
+          <t>220304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>271957</t>
+          <t>273325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>315776</t>
+          <t>315073</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>359672</t>
+          <t>362034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104091</t>
+          <t>104456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128536</t>
+          <t>128176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>429262</t>
+          <t>429755</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>480908</t>
+          <t>478880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>182717</t>
+          <t>180355</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>226613</t>
+          <t>227316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39246</t>
+          <t>39606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63691</t>
+          <t>63326</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>229263</t>
+          <t>231291</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>280909</t>
+          <t>280416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>767099</t>
+          <t>763443</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>837807</t>
+          <t>832083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>483070</t>
+          <t>483581</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>531582</t>
+          <t>530553</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1270810</t>
+          <t>1267736</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1348543</t>
+          <t>1344566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>400527</t>
+          <t>406251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>471235</t>
+          <t>474891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182703</t>
+          <t>183732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>231215</t>
+          <t>230704</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>604077</t>
+          <t>608054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>681810</t>
+          <t>684884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>185217</t>
+          <t>184911</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>223525</t>
+          <t>222810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>379341</t>
+          <t>379214</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>424079</t>
+          <t>424792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>578446</t>
+          <t>577338</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>635641</t>
+          <t>636425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127030</t>
+          <t>127745</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165338</t>
+          <t>165644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>143613</t>
+          <t>142900</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188351</t>
+          <t>188478</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282606</t>
+          <t>281822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>339801</t>
+          <t>340909</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>138331</t>
+          <t>137554</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>172121</t>
+          <t>171814</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>856557</t>
+          <t>854946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>920385</t>
+          <t>917681</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1006187</t>
+          <t>1004167</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1076167</t>
+          <t>1080139</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126080</t>
+          <t>126387</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>159870</t>
+          <t>160647</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>328375</t>
+          <t>331079</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>392203</t>
+          <t>393814</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>470793</t>
+          <t>466821</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>540773</t>
+          <t>542793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2006985</t>
+          <t>2012438</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2118644</t>
+          <t>2123701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2353144</t>
+          <t>2344268</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2451232</t>
+          <t>2452546</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4392089</t>
+          <t>4385553</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4542456</t>
+          <t>4538443</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1150712</t>
+          <t>1145655</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1262371</t>
+          <t>1256918</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>924518</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1023920</t>
+          <t>1032796</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2103964</t>
+          <t>2107977</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2254331</t>
+          <t>2260867</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>318973</t>
+          <t>317653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>355873</t>
+          <t>356422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>259610</t>
+          <t>259304</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>283884</t>
+          <t>283920</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>586517</t>
+          <t>588349</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>631111</t>
+          <t>631567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79237</t>
+          <t>78688</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116137</t>
+          <t>117457</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28635</t>
+          <t>28599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52909</t>
+          <t>53215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116518</t>
+          <t>116062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161112</t>
+          <t>159280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>293331</t>
+          <t>294083</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>331409</t>
+          <t>330974</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>247678</t>
+          <t>247926</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>280706</t>
+          <t>278783</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>552081</t>
+          <t>553292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>603684</t>
+          <t>602657</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,05%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86371</t>
+          <t>86806</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124449</t>
+          <t>123697</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54411</t>
+          <t>56334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87439</t>
+          <t>87191</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149213</t>
+          <t>150240</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200816</t>
+          <t>199605</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>445075</t>
+          <t>445769</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>487942</t>
+          <t>489244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>195140</t>
+          <t>195768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>221970</t>
+          <t>221988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>652701</t>
+          <t>648218</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>703789</t>
+          <t>701465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141473</t>
+          <t>140171</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>184340</t>
+          <t>183646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38159</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64989</t>
+          <t>64361</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>185755</t>
+          <t>188079</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>236843</t>
+          <t>241326</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>787098</t>
+          <t>785107</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>849226</t>
+          <t>849774</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>571529</t>
+          <t>573462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>621785</t>
+          <t>621053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1380476</t>
+          <t>1374781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1457434</t>
+          <t>1454490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>306762</t>
+          <t>306214</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368890</t>
+          <t>370881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141020</t>
+          <t>141752</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191276</t>
+          <t>189343</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>461359</t>
+          <t>464303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>538317</t>
+          <t>544012</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>336331</t>
+          <t>339377</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>377862</t>
+          <t>380064</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>573502</t>
+          <t>575364</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>620163</t>
+          <t>620940</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>920348</t>
+          <t>924665</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>985501</t>
+          <t>987249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131666</t>
+          <t>129464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173197</t>
+          <t>170151</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140209</t>
+          <t>139432</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186870</t>
+          <t>185008</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>284399</t>
+          <t>282651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>349552</t>
+          <t>345235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>117104</t>
+          <t>117366</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>150264</t>
+          <t>151485</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>845127</t>
+          <t>842755</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>902698</t>
+          <t>899735</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>971127</t>
+          <t>976549</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1042287</t>
+          <t>1040121</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116618</t>
+          <t>115397</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149778</t>
+          <t>149516</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>206653</t>
+          <t>209616</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>264224</t>
+          <t>266596</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>333946</t>
+          <t>336112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>405106</t>
+          <t>399684</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2372312</t>
+          <t>2373211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2482438</t>
+          <t>2483639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2766415</t>
+          <t>2767298</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2862267</t>
+          <t>2865881</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5171504</t>
+          <t>5172903</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5318948</t>
+          <t>5323110</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,54%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>932265</t>
+          <t>931064</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1042391</t>
+          <t>1041492</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>678026</t>
+          <t>674412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>773878</t>
+          <t>772995</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1636048</t>
+          <t>1631886</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1783492</t>
+          <t>1782093</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>320046</t>
+          <t>318546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>357214</t>
+          <t>355902</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>268935</t>
+          <t>268927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>297150</t>
+          <t>298428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>596667</t>
+          <t>597060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>643501</t>
+          <t>644997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71878</t>
+          <t>73190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>110546</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48899</t>
+          <t>47621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77114</t>
+          <t>77122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131640</t>
+          <t>130144</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>178474</t>
+          <t>178081</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>277139</t>
+          <t>277262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311328</t>
+          <t>309732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>274670</t>
+          <t>274809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>306912</t>
+          <t>305187</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>563776</t>
+          <t>565304</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>608055</t>
+          <t>609040</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,85%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64811</t>
+          <t>66407</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99000</t>
+          <t>98877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60999</t>
+          <t>62724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93241</t>
+          <t>93102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135995</t>
+          <t>135010</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180274</t>
+          <t>178746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>343669</t>
+          <t>344640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>387504</t>
+          <t>386206</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120054</t>
+          <t>120685</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142024</t>
+          <t>141160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>471663</t>
+          <t>474551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>519366</t>
+          <t>521768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134410</t>
+          <t>135708</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>178245</t>
+          <t>177274</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45129</t>
+          <t>44498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167730</t>
+          <t>165328</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215433</t>
+          <t>212545</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>777382</t>
+          <t>777829</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>839838</t>
+          <t>837499</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>600592</t>
+          <t>600981</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>649430</t>
+          <t>649264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1396541</t>
+          <t>1395478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1474303</t>
+          <t>1474421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,13%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>298810</t>
+          <t>301149</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361266</t>
+          <t>360819</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174418</t>
+          <t>174584</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>223256</t>
+          <t>222867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>488192</t>
+          <t>488074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>565954</t>
+          <t>567017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>420949</t>
+          <t>424644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>468479</t>
+          <t>469092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>551561</t>
+          <t>548922</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>595684</t>
+          <t>595706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>989106</t>
+          <t>989318</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1050011</t>
+          <t>1053671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,89%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148212</t>
+          <t>147599</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195742</t>
+          <t>192047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140407</t>
+          <t>140385</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>184530</t>
+          <t>187169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302771</t>
+          <t>299111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>363676</t>
+          <t>363464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>162969</t>
+          <t>160827</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>196747</t>
+          <t>193749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>784324</t>
+          <t>782501</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>842266</t>
+          <t>838394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>959037</t>
+          <t>958376</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1026746</t>
+          <t>1024546</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,23%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89313</t>
+          <t>92311</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123091</t>
+          <t>125233</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>233490</t>
+          <t>237362</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>291432</t>
+          <t>293255</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>335070</t>
+          <t>337270</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>402779</t>
+          <t>403440</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2384541</t>
+          <t>2384673</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2491044</t>
+          <t>2487409</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2666289</t>
+          <t>2672482</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2768926</t>
+          <t>2772422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5079833</t>
+          <t>5086086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5224452</t>
+          <t>5231360</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>877499</t>
+          <t>881134</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>984002</t>
+          <t>983870</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>745912</t>
+          <t>742416</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>848549</t>
+          <t>842356</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1658929</t>
+          <t>1652021</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1803548</t>
+          <t>1797295</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>486122</t>
+          <t>530889</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>476882</t>
+          <t>520800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>493732</t>
+          <t>538545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>440569</t>
+          <t>478634</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>434252</t>
+          <t>469083</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>444337</t>
+          <t>483780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>926691</t>
+          <t>1009523</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>914641</t>
+          <t>995881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>935309</t>
+          <t>1019262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>19729</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28330</t>
+          <t>29818</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>19328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25988</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38038</t>
+          <t>43148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>430661</t>
+          <t>461482</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>418620</t>
+          <t>449722</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>438133</t>
+          <t>469668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>370159</t>
+          <t>410675</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>360492</t>
+          <t>401265</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>375673</t>
+          <t>415853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>800821</t>
+          <t>872157</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>787703</t>
+          <t>858051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>811039</t>
+          <t>882959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20843</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32884</t>
+          <t>32769</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>20903</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>32502</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>21700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45511</t>
+          <t>46608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451504</t>
+          <t>482491</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451504</t>
+          <t>482491</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451504</t>
+          <t>482491</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381709</t>
+          <t>422168</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381709</t>
+          <t>422168</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381709</t>
+          <t>422168</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>904659</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>904659</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>904659</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>647127</t>
+          <t>448960</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>628299</t>
+          <t>436967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>661981</t>
+          <t>456772</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>158735</t>
+          <t>178678</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>153051</t>
+          <t>171973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162931</t>
+          <t>182808</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>805862</t>
+          <t>627637</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>788699</t>
+          <t>615099</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>824199</t>
+          <t>637835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>22652</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39965</t>
+          <t>34645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13860</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>29313</t>
+          <t>31472</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46476</t>
+          <t>44010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>969591</t>
+          <t>1061838</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>950824</t>
+          <t>1042278</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>984371</t>
+          <t>1078150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>939095</t>
+          <t>819520</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>922543</t>
+          <t>806942</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>959817</t>
+          <t>830357</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1908685</t>
+          <t>1881358</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1883582</t>
+          <t>1859227</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1940012</t>
+          <t>1899307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>63515</t>
+          <t>67114</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48735</t>
+          <t>50802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82282</t>
+          <t>86674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>38434</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54986</t>
+          <t>53698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>101949</t>
+          <t>108234</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70622</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>127052</t>
+          <t>130365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033106</t>
+          <t>1128952</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033106</t>
+          <t>1128952</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033106</t>
+          <t>1128952</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977529</t>
+          <t>860640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977529</t>
+          <t>860640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977529</t>
+          <t>860640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010634</t>
+          <t>1989592</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010634</t>
+          <t>1989592</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010634</t>
+          <t>1989592</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>437662</t>
+          <t>527707</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>420457</t>
+          <t>510601</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>449381</t>
+          <t>539073</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>801800</t>
+          <t>788969</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>788303</t>
+          <t>778571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>812054</t>
+          <t>799123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1239463</t>
+          <t>1316677</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1219133</t>
+          <t>1296923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1258746</t>
+          <t>1332660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36354</t>
+          <t>39175</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>27809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53559</t>
+          <t>56281</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38154</t>
+          <t>40461</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27900</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51651</t>
+          <t>50859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>74507</t>
+          <t>79635</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55224</t>
+          <t>63652</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94837</t>
+          <t>99389</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>839954</t>
+          <t>829430</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>839954</t>
+          <t>829430</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>839954</t>
+          <t>829430</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313970</t>
+          <t>1396312</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313970</t>
+          <t>1396312</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313970</t>
+          <t>1396312</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>213509</t>
+          <t>212503</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>187127</t>
+          <t>193489</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>226351</t>
+          <t>224010</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>718749</t>
+          <t>801945</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>700207</t>
+          <t>786472</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>729772</t>
+          <t>813110</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>932258</t>
+          <t>1014448</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>905557</t>
+          <t>992315</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>949889</t>
+          <t>1031837</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>24725</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53380</t>
+          <t>43739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>41541</t>
+          <t>41178</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30518</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60083</t>
+          <t>56651</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>68539</t>
+          <t>65903</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50908</t>
+          <t>48514</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95240</t>
+          <t>88036</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760290</t>
+          <t>843123</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760290</t>
+          <t>843123</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760290</t>
+          <t>843123</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000797</t>
+          <t>1080351</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000797</t>
+          <t>1080351</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000797</t>
+          <t>1080351</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3184673</t>
+          <t>3243379</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3146565</t>
+          <t>3205902</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3226942</t>
+          <t>3272207</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3429108</t>
+          <t>3478421</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3399829</t>
+          <t>3454700</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3455855</t>
+          <t>3500906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6613779</t>
+          <t>6721799</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6567601</t>
+          <t>6683069</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6666366</t>
+          <t>6758983</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>187937</t>
+          <t>194404</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>145668</t>
+          <t>165576</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226045</t>
+          <t>231881</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>144752</t>
+          <t>152847</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118005</t>
+          <t>130362</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>174031</t>
+          <t>176568</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>332690</t>
+          <t>347252</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>280103</t>
+          <t>310068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>378868</t>
+          <t>385982</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3372610</t>
+          <t>3437783</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3372610</t>
+          <t>3437783</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3372610</t>
+          <t>3437783</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573860</t>
+          <t>3631268</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573860</t>
+          <t>3631268</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573860</t>
+          <t>3631268</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6946469</t>
+          <t>7069051</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6946469</t>
+          <t>7069051</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6946469</t>
+          <t>7069051</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P36B08_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B08_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2007 (tasa de respuesta: 99,97%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2012 (tasa de respuesta: 99,78%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2016 (tasa de respuesta: 99,53%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2023 (tasa de respuesta: 99,86%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
